--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N48_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0001T0006Z000C1N48_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.226653900356381</v>
+        <v>0.5243312588079119</v>
       </c>
       <c r="D2" t="n">
-        <v>3.178491051881419</v>
+        <v>0.5165047959307306</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
